--- a/Data/EXCEL/Transfer/salemon/20240711/6416-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6416-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45B92CFA-1CB6-4877-BF2F-8FFA814A051A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25E4588D-326D-486C-AD36-4BD88274300E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{EC8C2C06-3252-456B-AA15-53B5B90CD97C}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{5D831ACA-0226-4FE2-93C1-6D1746478CD6}"/>
   </bookViews>
   <sheets>
     <sheet name="6416-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,22 +1261,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1DE4CB-0848-4FC2-B1D1-F5CD7FBFAA29}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02FBCEFF-29FD-45FA-A89A-7F4E4C3C678A}">
   <dimension ref="A1:Q290"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1303,7 +1303,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1385,7 +1385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1424,7 +1424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>-6.01</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>-14.3</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>-17.8</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>-22</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>-29.8</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>-19.100000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>-18.100000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>-18.5</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>-19.2</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>-16.8</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>-14.3</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>-12.3</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>-7.95</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>-4.46</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>-4.82</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>-15.2</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>7.76</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>9.0299999999999994</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>-3.1</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>-2.11</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>-9.1999999999999993</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>-14.7</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>-14.6</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>-14.5</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>-15.3</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>-16.600000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>-15.9</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>-13.6</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>-13.3</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>44317</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>-10.1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3491,7 +3491,7 @@
         <v>-8.9700000000000006</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>44256</v>
       </c>
@@ -3544,7 +3544,7 @@
         <v>-2.09</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>44197</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>-7.49</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>44136</v>
       </c>
@@ -3756,7 +3756,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>44075</v>
       </c>
@@ -3862,7 +3862,7 @@
         <v>36.6</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3915,7 +3915,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>44013</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4021,7 +4021,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>43952</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4127,7 +4127,7 @@
         <v>48.5</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>43891</v>
       </c>
@@ -4180,7 +4180,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>43831</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>43770</v>
       </c>
@@ -4392,7 +4392,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4445,7 +4445,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>43709</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>-1.01</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>-2.77</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>43647</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>-3.71</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4657,7 +4657,7 @@
         <v>-5.82</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>43586</v>
       </c>
@@ -4710,7 +4710,7 @@
         <v>-7.82</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>-9.02</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>43525</v>
       </c>
@@ -4816,7 +4816,7 @@
         <v>-5.29</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4869,7 +4869,7 @@
         <v>-7.4</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>43466</v>
       </c>
@@ -4922,7 +4922,7 @@
         <v>-7.19</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>43405</v>
       </c>
@@ -5028,7 +5028,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5081,7 +5081,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>43344</v>
       </c>
@@ -5134,7 +5134,7 @@
         <v>4.6399999999999997</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5187,7 +5187,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>43282</v>
       </c>
@@ -5240,7 +5240,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5293,7 +5293,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>43221</v>
       </c>
@@ -5346,7 +5346,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43191</v>
       </c>
@@ -5399,7 +5399,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>43160</v>
       </c>
@@ -5452,7 +5452,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>43132</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>6.64</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>43101</v>
       </c>
@@ -5558,7 +5558,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>43070</v>
       </c>
@@ -5611,7 +5611,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>43040</v>
       </c>
@@ -5664,7 +5664,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>43009</v>
       </c>
@@ -5717,7 +5717,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>42979</v>
       </c>
@@ -5770,7 +5770,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>42948</v>
       </c>
@@ -5823,7 +5823,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="10">
         <v>42917</v>
       </c>
@@ -5876,7 +5876,7 @@
         <v>-1.62</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>42887</v>
       </c>
@@ -5929,7 +5929,7 @@
         <v>-5.34</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="10">
         <v>42856</v>
       </c>
@@ -5982,7 +5982,7 @@
         <v>-11.8</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>42826</v>
       </c>
@@ -6035,7 +6035,7 @@
         <v>-13.4</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <v>42795</v>
       </c>
@@ -6088,7 +6088,7 @@
         <v>-13.3</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>42767</v>
       </c>
@@ -6141,7 +6141,7 @@
         <v>-22</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <v>42736</v>
       </c>
@@ -6194,7 +6194,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>42705</v>
       </c>
@@ -6247,7 +6247,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <v>42675</v>
       </c>
@@ -6300,7 +6300,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>42644</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>6.13</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="10">
         <v>42614</v>
       </c>
@@ -6406,7 +6406,7 @@
         <v>9.2100000000000009</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>42583</v>
       </c>
@@ -6459,7 +6459,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="10">
         <v>42552</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>42522</v>
       </c>
@@ -6565,7 +6565,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="10">
         <v>42491</v>
       </c>
@@ -6618,7 +6618,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>42461</v>
       </c>
@@ -6671,7 +6671,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="10">
         <v>42430</v>
       </c>
@@ -6724,7 +6724,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>42401</v>
       </c>
@@ -6777,7 +6777,7 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="10">
         <v>42370</v>
       </c>
@@ -6830,7 +6830,7 @@
         <v>53.4</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>42339</v>
       </c>
@@ -6883,7 +6883,7 @@
         <v>31.7</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="10">
         <v>42309</v>
       </c>
@@ -6936,7 +6936,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>42278</v>
       </c>
@@ -6989,7 +6989,7 @@
         <v>33.700000000000003</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="10">
         <v>42248</v>
       </c>
@@ -7042,7 +7042,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>42217</v>
       </c>
@@ -7095,7 +7095,7 @@
         <v>32.1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="10">
         <v>42186</v>
       </c>
@@ -7148,7 +7148,7 @@
         <v>33.4</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>42156</v>
       </c>
@@ -7201,7 +7201,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="10">
         <v>42125</v>
       </c>
@@ -7254,7 +7254,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>42095</v>
       </c>
@@ -7307,7 +7307,7 @@
         <v>46.5</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="10">
         <v>42064</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>42036</v>
       </c>
@@ -7413,7 +7413,7 @@
         <v>68.5</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="10">
         <v>42005</v>
       </c>
@@ -7466,7 +7466,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>41974</v>
       </c>
@@ -7519,7 +7519,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="10">
         <v>41944</v>
       </c>
@@ -7572,7 +7572,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>41913</v>
       </c>
@@ -7625,7 +7625,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="10">
         <v>41883</v>
       </c>
@@ -7678,7 +7678,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>41852</v>
       </c>
@@ -7731,7 +7731,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="10">
         <v>41821</v>
       </c>
@@ -7784,7 +7784,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>41791</v>
       </c>
@@ -7837,7 +7837,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="10">
         <v>41760</v>
       </c>
@@ -7890,7 +7890,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>41730</v>
       </c>
@@ -7943,7 +7943,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="10">
         <v>41699</v>
       </c>
@@ -7996,7 +7996,7 @@
         <v>-3.82</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>41671</v>
       </c>
@@ -8049,7 +8049,7 @@
         <v>-9.68</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="10">
         <v>41640</v>
       </c>
@@ -8102,7 +8102,7 @@
         <v>-18.899999999999999</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>41609</v>
       </c>
@@ -8155,7 +8155,7 @@
         <v>-3.68</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="10">
         <v>41579</v>
       </c>
@@ -8208,7 +8208,7 @@
         <v>-4.4400000000000004</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>41548</v>
       </c>
@@ -8261,7 +8261,7 @@
         <v>-1.72</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" s="10">
         <v>41518</v>
       </c>
@@ -8314,7 +8314,7 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" s="5">
         <v>41487</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" s="10">
         <v>41456</v>
       </c>
@@ -8420,7 +8420,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" s="5">
         <v>41426</v>
       </c>
@@ -8473,7 +8473,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" s="10">
         <v>41395</v>
       </c>
@@ -8526,7 +8526,7 @@
         <v>9.7799999999999994</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" s="5">
         <v>41365</v>
       </c>
@@ -8579,7 +8579,7 @@
         <v>7.68</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" s="10">
         <v>41334</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" s="5">
         <v>41306</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" s="10">
         <v>41275</v>
       </c>
@@ -8738,7 +8738,7 @@
         <v>-12.4</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" s="5">
         <v>41244</v>
       </c>
@@ -8791,737 +8791,737 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A183" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A184" s="10">
         <v>44317</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A186" s="10">
         <v>44256</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A187" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A188" s="10">
         <v>44197</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A189" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A190" s="10">
         <v>44136</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A191" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A192" s="10">
         <v>44075</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A193" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A194" s="10">
         <v>44013</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A195" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A196" s="10">
         <v>43952</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A197" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A198" s="10">
         <v>43891</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A199" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A200" s="10">
         <v>43831</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A202" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A203" s="10">
         <v>43770</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A204" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A205" s="10">
         <v>43709</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A206" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A207" s="10">
         <v>43647</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A208" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A209" s="10">
         <v>43586</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A210" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A211" s="10">
         <v>43525</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A212" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A213" s="10">
         <v>43466</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A214" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A215" s="10">
         <v>43405</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A216" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A217" s="10">
         <v>43344</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A218" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A219" s="10">
         <v>43282</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A221" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A222" s="10">
         <v>43221</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A223" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A224" s="10">
         <v>43160</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A225" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A226" s="10">
         <v>43101</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A227" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A228" s="10">
         <v>43040</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A229" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A230" s="10">
         <v>42979</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A231" s="5">
         <v>42948</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A232" s="10">
         <v>42917</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A233" s="5">
         <v>42887</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A234" s="10">
         <v>42856</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A235" s="5">
         <v>42826</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A236" s="10">
         <v>42795</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A237" s="5">
         <v>42767</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A238" s="10">
         <v>42736</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A240" s="5">
         <v>42705</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A241" s="10">
         <v>42675</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A242" s="5">
         <v>42644</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A243" s="10">
         <v>42614</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A244" s="5">
         <v>42583</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A245" s="10">
         <v>42552</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A246" s="5">
         <v>42522</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A247" s="10">
         <v>42491</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A248" s="5">
         <v>42461</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A249" s="10">
         <v>42430</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A250" s="5">
         <v>42401</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A251" s="10">
         <v>42370</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A252" s="5">
         <v>42339</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A253" s="10">
         <v>42309</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A254" s="5">
         <v>42278</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A255" s="10">
         <v>42248</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A256" s="5">
         <v>42217</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A257" s="10">
         <v>42186</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A258" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A259" s="5">
         <v>42156</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A260" s="10">
         <v>42125</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A261" s="5">
         <v>42095</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A262" s="10">
         <v>42064</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A263" s="5">
         <v>42036</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A264" s="10">
         <v>42005</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A265" s="5">
         <v>41974</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A266" s="10">
         <v>41944</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A267" s="5">
         <v>41913</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A268" s="10">
         <v>41883</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A269" s="5">
         <v>41852</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A270" s="10">
         <v>41821</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A271" s="5">
         <v>41791</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A272" s="10">
         <v>41760</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A273" s="5">
         <v>41730</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A274" s="10">
         <v>41699</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A275" s="5">
         <v>41671</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A276" s="10">
         <v>41640</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A278" s="5">
         <v>41609</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A279" s="10">
         <v>41579</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A280" s="5">
         <v>41548</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A281" s="10">
         <v>41518</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A282" s="5">
         <v>41487</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A283" s="10">
         <v>41456</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A284" s="5">
         <v>41426</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A285" s="10">
         <v>41395</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A286" s="5">
         <v>41365</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A287" s="10">
         <v>41334</v>
       </c>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A288" s="5">
         <v>41306</v>
       </c>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A289" s="10">
         <v>41275</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A290" s="5">
         <v>41244</v>
       </c>
